--- a/docs/xlsx/jobs-2026-09-20.xlsx
+++ b/docs/xlsx/jobs-2026-09-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,124 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Assistant Director for the Columbia Alumni Center</t>
+  </si>
+  <si>
+    <t>Columbia University, Office of Alumni Relations and Development</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e93599a3b8874290bbbef94887d6deaa-assistant-director-for-the-columbia-alumni-center-columbia-university-office-of-alumni-relations-and-development-new-york</t>
+  </si>
+  <si>
+    <t>Consultancy for Gender-Based Violence (GBV) Capacity Strengthening through an Interactive Cross-Departmental Bootcamp</t>
+  </si>
+  <si>
+    <t>St Andrew's Refugee Services</t>
+  </si>
+  <si>
+    <t>Cairo, C, EG</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 5000.00 - 5000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53ae47f521254a92beb24029ee18e3a0-consultancy-for-gender-based-violence-gbv-capacity-strengthening-through-an-interactive-cross-departmental-bootcamp-st-andrews-refugee-services-cairo</t>
+  </si>
+  <si>
+    <t>Consultancy for Gender-Based Violence (GBV) Services Staff Self-Care Retreat and Capacity Building</t>
+  </si>
+  <si>
+    <t>USD 1500.00 - 1500.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ceb54cb4fdc467ab943b10322c5d707-consultancy-for-gender-based-violence-gbv-services-staff-self-care-retreat-and-capacity-building-st-andrews-refugee-services-cairo</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Building One Community Corp</t>
+  </si>
+  <si>
+    <t>STAMFORD, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 70.00 - 80.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Immigrants Or Refugees, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d6d738915fd4e5182d951525ef23d8a-development-manager-building-one-community-corp-stamford</t>
+  </si>
+  <si>
+    <t>Intensive Case Manager</t>
+  </si>
+  <si>
+    <t>Prevention Point Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 46500.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b41ca21430b4792ae6d10ff307c051e-intensive-case-manager-prevention-point-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer, Columbia College and Arts &amp; Sciences</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e9ed3083f0b4772a2fb8b843165852b-major-gifts-officer-columbia-college-and-arts-sciences-columbia-university-office-of-alumni-relations-and-development-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Dancing Classrooms, Inc.</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3dfc10ebd34480f8bd6cfb0ea77a83c-program-manager-dancing-classrooms-inc-new-york</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +165,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +191,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +630,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +669,178 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-20.xlsx
+++ b/docs/xlsx/jobs-2026-09-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
   <si>
     <t>Title</t>
   </si>
@@ -107,6 +107,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/9d6d738915fd4e5182d951525ef23d8a-development-manager-building-one-community-corp-stamford</t>
+  </si>
+  <si>
+    <t>Director of Accounting and IT Infrastructure</t>
+  </si>
+  <si>
+    <t>Association for Middle Level Education</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ce8e6f953954026aaa76d054ec3776e-director-of-accounting-and-it-infrastructure-association-for-middle-level-education-westerville</t>
   </si>
   <si>
     <t>Intensive Case Manager</t>
@@ -630,7 +645,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -778,41 +793,41 @@
         <v>34</v>
       </c>
       <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -821,13 +836,36 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -840,6 +878,7 @@
     <hyperlink ref="H6" r:id="rId5"/>
     <hyperlink ref="H7" r:id="rId6"/>
     <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
